--- a/Excel/Producto.xlsx
+++ b/Excel/Producto.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajo\Muhia\Proyectos\sigem\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desarrollos\gippro\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F27870-2132-485D-A362-AE39B3CC88BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16815" windowHeight="8340"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Caja" sheetId="1" r:id="rId1"/>
@@ -24,57 +25,333 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
-  <si>
-    <t>kgbkj</t>
-  </si>
-  <si>
-    <t>fvdfs</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="107">
   <si>
     <t>Codigo</t>
   </si>
   <si>
-    <t>cesdwef</t>
-  </si>
-  <si>
-    <t>wrvs</t>
-  </si>
-  <si>
     <t>Cantidad</t>
   </si>
   <si>
     <t>Almacén</t>
   </si>
   <si>
-    <t>cwwe</t>
-  </si>
-  <si>
     <t>Nombre comercial</t>
   </si>
   <si>
-    <t>Ficha técnica</t>
-  </si>
-  <si>
-    <t>Producto final(Si o No)</t>
-  </si>
-  <si>
-    <t>Si</t>
-  </si>
-  <si>
-    <t>pepe</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>vfxvsvd</t>
+    <t>Formato</t>
+  </si>
+  <si>
+    <t>Planta</t>
+  </si>
+  <si>
+    <t>Costo</t>
+  </si>
+  <si>
+    <t>1 L</t>
+  </si>
+  <si>
+    <t>500 ML</t>
+  </si>
+  <si>
+    <t>Codigo 3 letras</t>
+  </si>
+  <si>
+    <t>Aceite de Cutícula</t>
+  </si>
+  <si>
+    <t>Acondicionador</t>
+  </si>
+  <si>
+    <t>Aromatizante</t>
+  </si>
+  <si>
+    <t>Autoescudo</t>
+  </si>
+  <si>
+    <t>Caja de madera chica</t>
+  </si>
+  <si>
+    <t>Caja de madera cuadrada</t>
+  </si>
+  <si>
+    <t>Caja de madera estrecha</t>
+  </si>
+  <si>
+    <t>Caja de madera Grande</t>
+  </si>
+  <si>
+    <t>Caja de madera mediana</t>
+  </si>
+  <si>
+    <t>Colonia</t>
+  </si>
+  <si>
+    <t>Combo 1</t>
+  </si>
+  <si>
+    <t>Combo 2</t>
+  </si>
+  <si>
+    <t>Combo 3</t>
+  </si>
+  <si>
+    <t>Combo 4</t>
+  </si>
+  <si>
+    <t>Combo 5</t>
+  </si>
+  <si>
+    <t>Combo 6</t>
+  </si>
+  <si>
+    <t>Combo Flor de Cuba</t>
+  </si>
+  <si>
+    <t>Desengrasante</t>
+  </si>
+  <si>
+    <t>Desengrasante Navy</t>
+  </si>
+  <si>
+    <t>Desengrasante Textil</t>
+  </si>
+  <si>
+    <t>Desincrustante</t>
+  </si>
+  <si>
+    <t>Desincrustante Ligero</t>
+  </si>
+  <si>
+    <t>Desincrustante Navy</t>
+  </si>
+  <si>
+    <t>Detergente blanqueador</t>
+  </si>
+  <si>
+    <t>Detergente Blanqueador</t>
+  </si>
+  <si>
+    <t>Detergente Concentrado</t>
+  </si>
+  <si>
+    <t>Detergente de fregar 1x4</t>
+  </si>
+  <si>
+    <t>Detergente de fregar Económico</t>
+  </si>
+  <si>
+    <t>Detergente de fregar gam alta</t>
+  </si>
+  <si>
+    <t>Detergente de Fregar gama alta</t>
+  </si>
+  <si>
+    <t>Detergente de fregar gama alta</t>
+  </si>
+  <si>
+    <t>Detergente de fregar gama media</t>
+  </si>
+  <si>
+    <t>Detergente para Fregar gama media</t>
+  </si>
+  <si>
+    <t>Detergente de Lavar Económico</t>
+  </si>
+  <si>
+    <t>Detergente de Lavar gama alta</t>
+  </si>
+  <si>
+    <t>Detergente para Lavar 240 ml</t>
+  </si>
+  <si>
+    <t>Detergente para Lavar gama alta</t>
+  </si>
+  <si>
+    <t>Detergente de lavar gama alta</t>
+  </si>
+  <si>
+    <t>Detergente de lavar gama media</t>
+  </si>
+  <si>
+    <t>Detergente para Lavar Gama Media</t>
+  </si>
+  <si>
+    <t>Detergente Pinaroma</t>
+  </si>
+  <si>
+    <t>Envase 1.5 L</t>
+  </si>
+  <si>
+    <t>Envases</t>
+  </si>
+  <si>
+    <t>Friega Suelos</t>
+  </si>
+  <si>
+    <t>Friega Suelos Plus</t>
+  </si>
+  <si>
+    <t>Gel anticalcáreo gama alta</t>
+  </si>
+  <si>
+    <t>Gel Anticalcáreo gama alta</t>
+  </si>
+  <si>
+    <t>Gel Anticalcáreo gama media</t>
+  </si>
+  <si>
+    <t>Gel de baño</t>
+  </si>
+  <si>
+    <t>Gel Higienizante de manos</t>
+  </si>
+  <si>
+    <t>Hojas de Papel Blanco</t>
+  </si>
+  <si>
+    <t>Lejía con Aceite de Pino</t>
+  </si>
+  <si>
+    <t>Lejía con aceite de pino</t>
+  </si>
+  <si>
+    <t>Limpia cristales</t>
+  </si>
+  <si>
+    <t>Limpia Cristales para Auto Env. 20 L</t>
+  </si>
+  <si>
+    <t>Limpia Cristales</t>
+  </si>
+  <si>
+    <t>Limpia cristales para carro</t>
+  </si>
+  <si>
+    <t>Limpiador de madera</t>
+  </si>
+  <si>
+    <t>Limpiador de Maderas 240</t>
+  </si>
+  <si>
+    <t>Líquido de freno</t>
+  </si>
+  <si>
+    <t>Destupidor para Cañerías Metálicas</t>
+  </si>
+  <si>
+    <t>Destupidor para Cañerías Plásticas</t>
+  </si>
+  <si>
+    <t>Loción para después de afeitar</t>
+  </si>
+  <si>
+    <t>Loción capilar con Hiel de Vaca (antipediculicida)</t>
+  </si>
+  <si>
+    <t>Loción capilar de aloe de vera</t>
+  </si>
+  <si>
+    <t>Mascarilla facial</t>
+  </si>
+  <si>
+    <t>Moldeador de Poligel</t>
+  </si>
+  <si>
+    <t>Neutralizador Navy</t>
+  </si>
+  <si>
+    <t>DESENGRASANTE</t>
+  </si>
+  <si>
+    <t>Pasta desengrasante para mecánicos</t>
+  </si>
+  <si>
+    <t>PASTA DESENGRASANTE</t>
+  </si>
+  <si>
+    <t>Refrigerante de carro</t>
+  </si>
+  <si>
+    <t>Repelente de insectos</t>
+  </si>
+  <si>
+    <t>Salfuman 240 ml</t>
+  </si>
+  <si>
+    <t>Salfuman</t>
+  </si>
+  <si>
+    <t>Sanitizante para uñas</t>
+  </si>
+  <si>
+    <t>Shampoo de carro</t>
+  </si>
+  <si>
+    <t>Shampoo sin sal</t>
+  </si>
+  <si>
+    <t>Shampoo sin sal de Aloe 340 ml</t>
+  </si>
+  <si>
+    <t>Loción higienizante</t>
+  </si>
+  <si>
+    <t>Suavizante textil</t>
+  </si>
+  <si>
+    <t>Suavizante textil 240 ml</t>
+  </si>
+  <si>
+    <t>Veneno para Roedores</t>
+  </si>
+  <si>
+    <t>40 ML</t>
+  </si>
+  <si>
+    <t>1 U</t>
+  </si>
+  <si>
+    <t>240 ML</t>
+  </si>
+  <si>
+    <t>340 ML</t>
+  </si>
+  <si>
+    <t>1500 ML</t>
+  </si>
+  <si>
+    <t>60 ML</t>
+  </si>
+  <si>
+    <t>750 ML</t>
+  </si>
+  <si>
+    <t>250 ML</t>
+  </si>
+  <si>
+    <t>0 KG</t>
+  </si>
+  <si>
+    <t>120 ML</t>
+  </si>
+  <si>
+    <t>A granel</t>
+  </si>
+  <si>
+    <t>5 L</t>
+  </si>
+  <si>
+    <t>20 L</t>
+  </si>
+  <si>
+    <t>XXX</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -84,9 +361,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color theme="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -109,18 +386,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -398,77 +680,2846 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" style="6" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>111</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>222</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>333</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>444</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>555</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>666</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="3">
+        <v>536</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>777</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>888</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3">
+        <v>55</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>999</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1091</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G10" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>1110</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>381.34</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>1221</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>51</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G12" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>1332</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="3">
+        <v>37</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>1443</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>17</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>1554</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>1665</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>1776</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3">
+        <v>38</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>1887</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3">
+        <v>91</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>1998</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="3">
+        <v>46</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>2109</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
+        <v>23</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>2220</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="3">
+        <v>50</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>2331</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3">
+        <v>23</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>2442</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3">
+        <v>46</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G23" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>2553</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>2664</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="3">
+        <v>100</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G25" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>2775</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>2886</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1150</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G27" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>2997</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="3">
+        <v>268.5</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G28" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>3108</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="3">
+        <v>749.5</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G29" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>3219</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30" s="3">
+        <v>100</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>3330</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>3441</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G32" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>3552</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3">
+        <v>200</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G33" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>3663</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E34" s="3">
+        <v>3.75</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G34" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>3774</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G35" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>3885</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" s="3">
+        <v>68</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>3996</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E37" s="3">
+        <v>28.8</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G37" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>4107</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E38" s="3">
+        <v>479</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G38" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>4218</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E39" s="3">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G39" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>4329</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G40" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>4440</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G41" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>4551</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>4662</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3">
+        <v>22</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G43" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>4773</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>4884</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
+        <v>561</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G45" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>4995</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>5106</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3">
+        <v>484</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G47" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>5217</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G48" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>5328</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>5439</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E50" s="3">
+        <v>24</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G50" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>5550</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E51" s="3">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G51" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>5661</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3">
+        <v>840.5</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G52" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>5772</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E53" s="3">
+        <v>25</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G53" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>5883</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" s="3">
+        <v>626</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G54" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>5994</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E55" s="3">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G55" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>6105</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E56" s="3">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G56" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>6216</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3">
+        <v>623</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G57" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>6327</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E58" s="3">
+        <v>972</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G58" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>6438</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3">
+        <v>10980</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G59" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>6549</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3184</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G60" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>6660</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E61" s="3">
+        <v>28.8</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G61" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>6771</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2746</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G62" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>6882</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E63" s="3">
+        <v>213</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G63" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>6993</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E64" s="3">
+        <v>4</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G64" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>7104</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E65" s="3">
+        <v>82</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G65" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>7215</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66" s="3">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>7326</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E67" s="3">
+        <v>224</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G67" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>7437</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E68" s="3">
+        <v>307.5</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G68" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>7548</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E69" s="3">
+        <v>150</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G69" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>7659</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G70" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>7770</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E71" s="3">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G71" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>7881</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3">
+        <v>553.5</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G72" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>7992</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E73" s="3">
+        <v>1716</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G73" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>8103</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E74" s="3">
+        <v>27</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G74" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>8214</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E75" s="3">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G75" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>8325</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G76" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>8436</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E77" s="3">
+        <v>1131</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G77" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>8547</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E78" s="3">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G78" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>8658</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E79" s="3">
+        <v>29</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G79" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>8769</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E80" s="3">
+        <v>194</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G80" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>8880</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>8991</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E82" s="3">
+        <v>69</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G82" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>9102</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1967</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G83" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>9213</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E84" s="3">
+        <v>36</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G84" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>9324</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E85" s="3">
+        <v>14</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G85" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>9435</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E86" s="3">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G86" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>9546</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E87" s="3">
+        <v>0</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G87" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>9657</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E88" s="3">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G88" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>9768</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3">
+        <v>156</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G89" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>9879</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E90" s="3">
+        <v>39.5</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G90" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>9990</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>10101</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E92" s="3">
+        <v>0</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G92" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>10212</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E93" s="3">
+        <v>80</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G93" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>10323</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3">
+        <v>319</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G94" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>10434</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E95" s="3">
+        <v>1376</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G95" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>10545</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G96" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>10656</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E97" s="3">
+        <v>636</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G97" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>10767</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E98" s="3">
+        <v>13</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G98" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>10878</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E99" s="3">
+        <v>5</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G99" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>10989</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G100" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>11100</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G101" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>11211</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="F102" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
+      <c r="G102" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>11322</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E103" s="3">
+        <v>0</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G103" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>11433</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E104" s="3">
+        <v>0</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G104" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>11544</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E105" s="3">
+        <v>701.5</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G105" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>11655</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E106" s="3">
+        <v>0</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G106" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>11766</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E107" s="3">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G107" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>11877</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E108" s="3">
+        <v>0</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G108" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>11988</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E109" s="3">
+        <v>0</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G109" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
+        <v>12099</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E110" s="3">
+        <v>36</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G110" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="6">
+        <v>12210</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E111" s="3">
+        <v>5</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G111" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="6">
+        <v>12321</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E112" s="3">
+        <v>258.5</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G112" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="6">
+        <v>12432</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E113" s="3">
+        <v>0</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G113" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="6">
+        <v>12543</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E114" s="3">
+        <v>1219.5</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G114" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="6">
+        <v>12654</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E115" s="3">
+        <v>0</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G115" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="6">
+        <v>12765</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E116" s="3">
+        <v>88</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G116" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="6">
+        <v>12876</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E117" s="3">
+        <v>895.5</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G117" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
+        <v>12987</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E118" s="3">
+        <v>0</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G118" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="6">
+        <v>13098</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E119" s="3">
+        <v>170</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G119" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
+        <v>13209</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E120" s="3">
+        <v>1</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G120" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
+        <v>13320</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E121" s="3">
+        <v>314.5</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G121" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
+        <v>13431</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E122" s="3">
+        <v>0</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G122" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="6">
+        <v>13542</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E123" s="3">
+        <v>921</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G123" s="6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
